--- a/UR OCTOBER 2026/od_matrix_october2026.xlsx
+++ b/UR OCTOBER 2026/od_matrix_october2026.xlsx
@@ -483,7 +483,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Coverage 1-16 Oct 2026 (track export window). 10 Oct: no recorded departures — see PDF.</t>
+          <t>Coverage 1-16 Oct 2026 (track export window).</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 — 25 sectors</t>
+          <t>2026-10-09 — 26 sectors</t>
         </is>
       </c>
     </row>
@@ -1526,8 +1526,11 @@
           <t>LGW</t>
         </is>
       </c>
+      <c r="B12" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q12" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1609,7 +1612,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C19" s="5" t="n">
         <v>1</v>
@@ -1654,7 +1657,7 @@
         <v>1</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1693,7 +1696,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10 — 0 sectors (no recorded departures)</t>
+          <t>2026-10-10 — 17 sectors</t>
         </is>
       </c>
     </row>
@@ -1790,8 +1793,32 @@
           <t>EBB</t>
         </is>
       </c>
+      <c r="D4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="Q4" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -1820,8 +1847,11 @@
           <t>DAR</t>
         </is>
       </c>
+      <c r="B7" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q7" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1830,8 +1860,11 @@
           <t>HRE</t>
         </is>
       </c>
+      <c r="B8" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q8" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1840,8 +1873,11 @@
           <t>JNB</t>
         </is>
       </c>
+      <c r="B9" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q9" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1860,8 +1896,11 @@
           <t>JUB</t>
         </is>
       </c>
+      <c r="B11" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1880,8 +1919,11 @@
           <t>LOS</t>
         </is>
       </c>
+      <c r="B13" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1890,8 +1932,11 @@
           <t>LUN</t>
         </is>
       </c>
+      <c r="B14" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1910,8 +1955,11 @@
           <t>MGQ</t>
         </is>
       </c>
+      <c r="B16" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q16" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1920,8 +1968,11 @@
           <t>NBO</t>
         </is>
       </c>
+      <c r="B17" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1941,28 +1992,28 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="5" t="n">
         <v>0</v>
@@ -1971,22 +2022,22 @@
         <v>0</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -4310,7 +4361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D266"/>
+  <dimension ref="A1:D283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7443,7 +7494,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>LGW</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -7463,7 +7514,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -7483,7 +7534,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>MGQ</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -7503,7 +7554,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>MGQ</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -7512,18 +7563,18 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -7532,18 +7583,18 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>BOM</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -7558,17 +7609,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>BOM</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -7578,17 +7629,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
           <t>DAR</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>NBO</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -7598,7 +7649,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7608,7 +7659,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -7618,7 +7669,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7628,7 +7679,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -7638,7 +7689,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7648,7 +7699,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -7658,7 +7709,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7668,7 +7719,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -7678,7 +7729,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7688,7 +7739,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>LGW</t>
+          <t>MGQ</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -7698,7 +7749,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7708,27 +7759,27 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -7738,17 +7789,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -7758,17 +7809,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>MGQ</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -7778,37 +7829,37 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>ZNZ</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -7818,12 +7869,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>MGQ</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -7838,12 +7889,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>JRO</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -7863,7 +7914,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -7883,7 +7934,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>BOM</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -7903,7 +7954,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>MGQ</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -7923,32 +7974,32 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
           <t>NBO</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>EBB</t>
-        </is>
-      </c>
       <c r="D181" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
           <t>BJM</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>EBB</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -7958,27 +8009,27 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
           <t>DAR</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>EBB</t>
-        </is>
-      </c>
       <c r="D183" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -7988,7 +8039,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -7998,7 +8049,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8008,17 +8059,17 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8028,17 +8079,17 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>LGW</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8048,7 +8099,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -8058,7 +8109,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8068,7 +8119,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -8078,7 +8129,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8088,7 +8139,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -8098,7 +8149,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8108,62 +8159,62 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>MGQ</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>ZNZ</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -8178,12 +8229,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>JRO</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -8198,17 +8249,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -8218,12 +8269,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -8232,18 +8283,18 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>MGQ</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -8258,12 +8309,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -8272,23 +8323,23 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -8298,27 +8349,27 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -8328,7 +8379,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -8338,7 +8389,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -8348,17 +8399,17 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -8368,17 +8419,17 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -8388,7 +8439,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>LGW</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -8398,7 +8449,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -8408,7 +8459,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>MGQ</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -8418,7 +8469,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -8428,37 +8479,37 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -8468,7 +8519,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -8478,7 +8529,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -8492,13 +8543,13 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -8508,7 +8559,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -8518,12 +8569,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>LGW</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -8538,7 +8589,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -8548,7 +8599,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -8558,12 +8609,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>MGQ</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -8572,7 +8623,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="214">
@@ -8583,7 +8634,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -8592,18 +8643,18 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -8618,7 +8669,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -8638,7 +8689,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -8648,7 +8699,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>BOM</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8658,7 +8709,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -8668,7 +8719,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8678,7 +8729,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -8688,7 +8739,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8698,7 +8749,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -8708,7 +8759,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -8718,7 +8769,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -8728,7 +8779,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>LGW</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -8738,7 +8789,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -8748,7 +8799,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>MGQ</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -8758,7 +8809,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -8778,17 +8829,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>ZNZ</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -8798,7 +8849,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -8818,7 +8869,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -8832,23 +8883,23 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>JRO</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -8858,12 +8909,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>LGW</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8878,7 +8929,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -8898,12 +8949,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>MGQ</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8918,7 +8969,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -8932,7 +8983,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="232">
@@ -8943,12 +8994,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>ZNZ</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>JRO</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -8958,17 +9009,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
           <t>BJM</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>EBB</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -8978,17 +9029,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
           <t>BOM</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>EBB</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -8998,17 +9049,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
           <t>DAR</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>EBB</t>
         </is>
       </c>
       <c r="D235" t="n">
@@ -9018,7 +9069,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -9028,7 +9079,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -9038,7 +9089,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -9048,7 +9099,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="D237" t="n">
@@ -9058,7 +9109,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -9068,7 +9119,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="D238" t="n">
@@ -9078,7 +9129,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -9088,7 +9139,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="D239" t="n">
@@ -9098,7 +9149,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -9108,17 +9159,17 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -9128,7 +9179,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>ZNZ</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -9138,32 +9189,32 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -9172,18 +9223,18 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>JRO</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -9198,12 +9249,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -9212,18 +9263,18 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -9238,12 +9289,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -9258,17 +9309,17 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D248" t="n">
@@ -9278,17 +9329,17 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>ZNZ</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>JRO</t>
         </is>
       </c>
       <c r="D249" t="n">
@@ -9298,17 +9349,17 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -9318,17 +9369,17 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>BOM</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D251" t="n">
@@ -9338,17 +9389,17 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>LGW</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D252" t="n">
@@ -9358,7 +9409,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -9368,7 +9419,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="D253" t="n">
@@ -9378,7 +9429,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -9388,7 +9439,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D254" t="n">
@@ -9398,7 +9449,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -9408,7 +9459,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="D255" t="n">
@@ -9418,7 +9469,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -9428,7 +9479,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>MGQ</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="D256" t="n">
@@ -9438,7 +9489,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -9448,17 +9499,17 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -9468,7 +9519,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>ZNZ</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="D258" t="n">
@@ -9478,17 +9529,17 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="D259" t="n">
@@ -9498,12 +9549,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>JRO</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9518,12 +9569,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -9538,12 +9589,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -9552,7 +9603,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="263">
@@ -9563,7 +9614,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -9583,7 +9634,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>MGQ</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -9603,16 +9654,16 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="266">
@@ -9623,15 +9674,355 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>JNB</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>JUB</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>LGW</t>
+        </is>
+      </c>
+      <c r="D269" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>LOS</t>
+        </is>
+      </c>
+      <c r="D270" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>LUN</t>
+        </is>
+      </c>
+      <c r="D271" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="D272" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>MGQ</t>
+        </is>
+      </c>
+      <c r="D273" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>NBO</t>
+        </is>
+      </c>
+      <c r="D274" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
           <t>ZNZ</t>
         </is>
       </c>
-      <c r="C266" t="inlineStr">
+      <c r="D275" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>JNB</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D276" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
         <is>
           <t>JRO</t>
         </is>
       </c>
-      <c r="D266" t="n">
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D277" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>JUB</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D278" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>LOS</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D279" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D280" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>MGQ</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D281" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>NBO</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D282" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>ZNZ</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>JRO</t>
+        </is>
+      </c>
+      <c r="D283" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10038,19 +10429,19 @@
         <v>14</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="I4" s="4" t="n">
         <v>16</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>15</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>7</v>
@@ -10059,22 +10450,22 @@
         <v>10</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M4" s="4" t="n">
         <v>7</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P4" s="4" t="n">
         <v>7</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>152</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5">
@@ -10110,13 +10501,13 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O7" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -10126,13 +10517,13 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L8" s="4" t="n">
         <v>6</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -10142,10 +10533,10 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -10168,13 +10559,13 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O11" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -10184,10 +10575,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -10197,10 +10588,10 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -10210,13 +10601,13 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>3</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -10239,10 +10630,10 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -10252,10 +10643,10 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -10278,28 +10669,28 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="C19" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>5</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J19" s="5" t="n">
         <v>7</v>
@@ -10308,22 +10699,22 @@
         <v>10</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>7</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P19" s="5" t="n">
         <v>7</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>317</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>

--- a/UR OCTOBER 2026/od_matrix_october2026.xlsx
+++ b/UR OCTOBER 2026/od_matrix_october2026.xlsx
@@ -26,7 +26,9 @@
     <sheet name="2026-10-14" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="2026-10-15" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="2026-10-16" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="DIVERSION_CHECK" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="2026-10-17" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="2026-10-18" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="DIVERSION_CHECK" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Coverage 1-16 Oct 2026 (track export window).</t>
+          <t>Coverage 1-18 Oct 2026 (track export window).</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3993,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 — 25 sectors</t>
+          <t>2026-10-16 — 26 sectors</t>
         </is>
       </c>
     </row>
@@ -4216,8 +4218,11 @@
           <t>LGW</t>
         </is>
       </c>
+      <c r="B12" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q12" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -4302,7 +4307,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C19" s="5" t="n">
         <v>1</v>
@@ -4347,7 +4352,7 @@
         <v>1</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -4361,7 +4366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D283"/>
+  <dimension ref="A1:D307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9934,7 +9939,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>LGW</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -9954,7 +9959,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -9974,7 +9979,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>MGQ</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -9994,7 +9999,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>MGQ</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -10003,7 +10008,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="283">
@@ -10014,15 +10019,495 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
+          <t>NBO</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D283" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
           <t>ZNZ</t>
         </is>
       </c>
-      <c r="C283" t="inlineStr">
+      <c r="C284" t="inlineStr">
         <is>
           <t>JRO</t>
         </is>
       </c>
-      <c r="D283" t="n">
+      <c r="D284" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D285" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>BOM</t>
+        </is>
+      </c>
+      <c r="D286" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="D287" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>HRE</t>
+        </is>
+      </c>
+      <c r="D288" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>JNB</t>
+        </is>
+      </c>
+      <c r="D289" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>JUB</t>
+        </is>
+      </c>
+      <c r="D290" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>LUN</t>
+        </is>
+      </c>
+      <c r="D291" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>NBO</t>
+        </is>
+      </c>
+      <c r="D292" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>HRE</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D293" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>JNB</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D294" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>JUB</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D295" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>LOS</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D296" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>LUN</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D297" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>NBO</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D298" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>BOM</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D299" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D300" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="D301" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>LGW</t>
+        </is>
+      </c>
+      <c r="D302" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>LOS</t>
+        </is>
+      </c>
+      <c r="D303" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>MGQ</t>
+        </is>
+      </c>
+      <c r="D304" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>NBO</t>
+        </is>
+      </c>
+      <c r="D305" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>ZNZ</t>
+        </is>
+      </c>
+      <c r="D306" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>NBO</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D307" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10032,6 +10517,739 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="6" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17 — 15 sectors</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>from \ to</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>BJM</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>BOM</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>HRE</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>JNB</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>JRO</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>JUB</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>LGW</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>LOS</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>LUN</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>MGQ</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>NBO</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>ZNZ</t>
+        </is>
+      </c>
+      <c r="Q3" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL OUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>BJM</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>BOM</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>HRE</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>JNB</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>JRO</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>JUB</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>LGW</t>
+        </is>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>LOS</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>LUN</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="Q15" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>MGQ</t>
+        </is>
+      </c>
+      <c r="Q16" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>NBO</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ZNZ</t>
+        </is>
+      </c>
+      <c r="Q18" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL IN</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="5" t="n">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="6" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18 — 9 sectors</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>from \ to</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>BJM</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>BOM</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>HRE</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>JNB</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>JRO</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>JUB</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>LGW</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>LOS</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>LUN</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>MGQ</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>NBO</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>ZNZ</t>
+        </is>
+      </c>
+      <c r="Q3" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL OUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>BJM</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>BOM</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>HRE</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>JNB</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>JRO</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>JUB</t>
+        </is>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>LGW</t>
+        </is>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>LOS</t>
+        </is>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>LUN</t>
+        </is>
+      </c>
+      <c r="Q14" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="Q15" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>MGQ</t>
+        </is>
+      </c>
+      <c r="Q16" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>NBO</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ZNZ</t>
+        </is>
+      </c>
+      <c r="Q18" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL IN</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10328,7 +11546,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>October 2026 (1-16 Oct) — all sectors</t>
+          <t>October 2026 (1-18 Oct) — all sectors</t>
         </is>
       </c>
     </row>
@@ -10429,43 +11647,43 @@
         <v>14</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="I4" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="F4" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>16</v>
-      </c>
       <c r="J4" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K4" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="L4" s="4" t="n">
         <v>10</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>9</v>
       </c>
       <c r="M4" s="4" t="n">
         <v>7</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>161</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5">
@@ -10488,10 +11706,10 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -10501,13 +11719,13 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O7" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -10517,13 +11735,13 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L8" s="4" t="n">
         <v>6</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -10533,10 +11751,10 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -10559,13 +11777,13 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O11" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
@@ -10575,10 +11793,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -10588,10 +11806,10 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -10601,13 +11819,13 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>3</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -10643,10 +11861,10 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -10669,52 +11887,52 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="C19" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>5</v>
       </c>
       <c r="I19" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="L19" s="5" t="n">
         <v>16</v>
-      </c>
-      <c r="J19" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="K19" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v>15</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>7</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>335</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>

--- a/UR OCTOBER 2026/od_matrix_october2026.xlsx
+++ b/UR OCTOBER 2026/od_matrix_october2026.xlsx
@@ -28,7 +28,8 @@
     <sheet name="2026-10-16" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="2026-10-17" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="2026-10-18" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="DIVERSION_CHECK" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="2026-10-19" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="DIVERSION_CHECK" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -485,7 +486,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Coverage 1-18 Oct 2026 (track export window).</t>
+          <t>Coverage 1-19 Oct 2026 (track export window).</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D307"/>
+  <dimension ref="A1:D326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10339,7 +10340,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>BOM</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -10359,7 +10360,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>BOM</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -10379,16 +10380,16 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="302">
@@ -10404,7 +10405,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>LGW</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="D302" t="n">
@@ -10424,7 +10425,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D303" t="n">
@@ -10444,7 +10445,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>MGQ</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="D304" t="n">
@@ -10464,7 +10465,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="D305" t="n">
@@ -10484,7 +10485,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>ZNZ</t>
+          <t>LGW</t>
         </is>
       </c>
       <c r="D306" t="n">
@@ -10499,16 +10500,396 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>LOS</t>
+        </is>
+      </c>
+      <c r="D307" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>LUN</t>
+        </is>
+      </c>
+      <c r="D308" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="D309" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>MGQ</t>
+        </is>
+      </c>
+      <c r="D310" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
           <t>NBO</t>
         </is>
       </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>EBB</t>
-        </is>
-      </c>
-      <c r="D307" t="n">
-        <v>1</v>
+      <c r="D311" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>ZNZ</t>
+        </is>
+      </c>
+      <c r="D312" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>JRO</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D313" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>JUB</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D314" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>LGW</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D315" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>LOS</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D316" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D317" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>MGQ</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D318" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>NBO</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D319" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>JNB</t>
+        </is>
+      </c>
+      <c r="D320" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>JUB</t>
+        </is>
+      </c>
+      <c r="D321" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>LOS</t>
+        </is>
+      </c>
+      <c r="D322" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>NBO</t>
+        </is>
+      </c>
+      <c r="D323" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>HRE</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D324" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>JNB</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D325" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>NBO</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D326" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -10921,7 +11302,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 — 9 sectors</t>
+          <t>2026-10-18 — 26 sectors</t>
         </is>
       </c>
     </row>
@@ -11018,26 +11399,41 @@
           <t>EBB</t>
         </is>
       </c>
+      <c r="C4" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="E4" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="G4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="J4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="L4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="N4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -11046,8 +11442,11 @@
           <t>BJM</t>
         </is>
       </c>
+      <c r="B5" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q5" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -11070,10 +11469,10 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -11102,8 +11501,11 @@
           <t>JRO</t>
         </is>
       </c>
+      <c r="B10" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q10" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -11112,8 +11514,11 @@
           <t>JUB</t>
         </is>
       </c>
+      <c r="B11" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -11122,8 +11527,11 @@
           <t>LGW</t>
         </is>
       </c>
+      <c r="B12" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q12" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -11132,8 +11540,11 @@
           <t>LOS</t>
         </is>
       </c>
+      <c r="B13" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -11152,8 +11563,11 @@
           <t>MBA</t>
         </is>
       </c>
+      <c r="B15" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q15" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -11162,8 +11576,11 @@
           <t>MGQ</t>
         </is>
       </c>
+      <c r="B16" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q16" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -11173,10 +11590,10 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -11196,52 +11613,52 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="P19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -11250,6 +11667,359 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="6" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 — 8 sectors</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>from \ to</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>BJM</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>BOM</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>HRE</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>JNB</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>JRO</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>JUB</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>LGW</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>LOS</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>LUN</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>MGQ</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>NBO</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>ZNZ</t>
+        </is>
+      </c>
+      <c r="Q3" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL OUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>BJM</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>BOM</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>HRE</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>JNB</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>JRO</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>JUB</t>
+        </is>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>LGW</t>
+        </is>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>LOS</t>
+        </is>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>LUN</t>
+        </is>
+      </c>
+      <c r="Q14" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="Q15" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>MGQ</t>
+        </is>
+      </c>
+      <c r="Q16" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>NBO</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ZNZ</t>
+        </is>
+      </c>
+      <c r="Q18" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL IN</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11546,7 +12316,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>October 2026 (1-18 Oct) — all sectors</t>
+          <t>October 2026 (1-19 Oct) — all sectors</t>
         </is>
       </c>
     </row>
@@ -11644,7 +12414,7 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>5</v>
@@ -11656,34 +12426,34 @@
         <v>10</v>
       </c>
       <c r="G4" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="I4" s="4" t="n">
         <v>19</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>17</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K4" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L4" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="L4" s="4" t="n">
-        <v>10</v>
-      </c>
       <c r="M4" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N4" s="4" t="n">
         <v>10</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="P4" s="4" t="n">
         <v>8</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>175</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5">
@@ -11693,10 +12463,10 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -11719,13 +12489,13 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O7" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -11735,13 +12505,13 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L8" s="4" t="n">
         <v>6</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -11751,10 +12521,10 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -11764,10 +12534,10 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -11777,13 +12547,13 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O11" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
@@ -11793,10 +12563,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -11806,10 +12576,10 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
@@ -11835,10 +12605,10 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -11848,10 +12618,10 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -11861,10 +12631,10 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18">
@@ -11887,10 +12657,10 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>5</v>
@@ -11902,37 +12672,37 @@
         <v>13</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>5</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J19" s="5" t="n">
         <v>8</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N19" s="5" t="n">
         <v>10</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P19" s="5" t="n">
         <v>8</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>360</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>

--- a/UR OCTOBER 2026/od_matrix_october2026.xlsx
+++ b/UR OCTOBER 2026/od_matrix_october2026.xlsx
@@ -1304,7 +1304,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 — 26 sectors</t>
+          <t>2026-10-09 — 28 sectors</t>
         </is>
       </c>
     </row>
@@ -1555,8 +1555,11 @@
           <t>LUN</t>
         </is>
       </c>
+      <c r="F14" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1604,8 +1607,11 @@
           <t>ZNZ</t>
         </is>
       </c>
+      <c r="H18" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q18" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1627,13 +1633,13 @@
         <v>1</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>1</v>
@@ -1660,7 +1666,7 @@
         <v>1</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1699,7 +1705,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10 — 17 sectors</t>
+          <t>2026-10-10 — 19 sectors</t>
         </is>
       </c>
     </row>
@@ -1866,8 +1872,11 @@
       <c r="B8" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="L8" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q8" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -1938,8 +1947,11 @@
       <c r="B14" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="F14" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q14" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -2007,7 +2019,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>1</v>
@@ -2025,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>0</v>
@@ -2040,7 +2052,7 @@
         <v>0</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -2079,7 +2091,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11 — 26 sectors</t>
+          <t>2026-10-11 — 30 sectors</t>
         </is>
       </c>
     </row>
@@ -2310,8 +2322,11 @@
           <t>LGW</t>
         </is>
       </c>
+      <c r="B12" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q12" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -2333,8 +2348,11 @@
           <t>LUN</t>
         </is>
       </c>
+      <c r="F14" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -2343,8 +2361,11 @@
           <t>MBA</t>
         </is>
       </c>
+      <c r="B15" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q15" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -2379,8 +2400,11 @@
           <t>ZNZ</t>
         </is>
       </c>
+      <c r="H18" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q18" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -2390,7 +2414,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C19" s="5" t="n">
         <v>1</v>
@@ -2402,13 +2426,13 @@
         <v>1</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>1</v>
@@ -2435,7 +2459,7 @@
         <v>1</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -3623,7 +3647,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 — 15 sectors</t>
+          <t>2026-10-15 — 16 sectors</t>
         </is>
       </c>
     </row>
@@ -3790,8 +3814,11 @@
           <t>HRE</t>
         </is>
       </c>
+      <c r="L8" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q8" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -3940,7 +3967,7 @@
         <v>1</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>0</v>
@@ -3955,7 +3982,7 @@
         <v>0</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -4367,7 +4394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D326"/>
+  <dimension ref="A1:D349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5340,12 +5367,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -5360,7 +5387,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5380,7 +5407,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5400,7 +5427,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5420,7 +5447,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MGQ</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -5440,12 +5467,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -5455,12 +5482,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>MGQ</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -5475,12 +5502,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BOM</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -5500,7 +5527,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5509,7 +5536,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -5520,12 +5547,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>BOM</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -5540,16 +5567,16 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -5565,7 +5592,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -5585,7 +5612,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -5605,7 +5632,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>LGW</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -5625,7 +5652,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -5645,7 +5672,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MGQ</t>
+          <t>LGW</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -5665,11 +5692,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -5685,7 +5712,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ZNZ</t>
+          <t>MGQ</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -5700,16 +5727,16 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -5720,12 +5747,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JRO</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>ZNZ</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -5740,7 +5767,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5760,7 +5787,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>LGW</t>
+          <t>JRO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5780,7 +5807,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5800,7 +5827,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MGQ</t>
+          <t>LGW</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5820,7 +5847,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5829,7 +5856,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -5840,12 +5867,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ZNZ</t>
+          <t>MGQ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>JRO</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -5855,12 +5882,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5869,23 +5896,23 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>ZNZ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JRO</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -5900,12 +5927,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -5920,12 +5947,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -5945,7 +5972,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -5965,7 +5992,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -5985,7 +6012,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -6005,11 +6032,11 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -6025,7 +6052,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -6045,7 +6072,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -6060,12 +6087,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -6080,12 +6107,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -6100,7 +6127,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6120,7 +6147,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6129,7 +6156,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
@@ -6140,12 +6167,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -6160,7 +6187,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6180,12 +6207,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -6195,12 +6222,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6215,12 +6242,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6229,7 +6256,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -6240,12 +6267,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -6260,12 +6287,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -6285,7 +6312,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -6305,11 +6332,11 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -6325,7 +6352,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -6345,11 +6372,11 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>LGW</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
@@ -6365,7 +6392,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MGQ</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -6385,11 +6412,11 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>LGW</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -6400,12 +6427,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>MGQ</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -6420,16 +6447,16 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -6440,7 +6467,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6460,12 +6487,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -6480,7 +6507,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>LGW</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6500,7 +6527,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6520,7 +6547,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>MGQ</t>
+          <t>LGW</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6540,7 +6567,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6549,18 +6576,18 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>MGQ</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6575,21 +6602,21 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -6600,12 +6627,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>BOM</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -6625,7 +6652,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -6645,7 +6672,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>BOM</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -6665,7 +6692,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -6685,7 +6712,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -6705,7 +6732,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -6725,11 +6752,11 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -6745,7 +6772,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ZNZ</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -6760,16 +6787,16 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
@@ -6780,16 +6807,16 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>ZNZ</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -6800,12 +6827,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>JRO</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -6820,7 +6847,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -6829,7 +6856,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124">
@@ -6840,7 +6867,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>JRO</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -6860,7 +6887,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -6880,7 +6907,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -6900,12 +6927,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ZNZ</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>JRO</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -6915,12 +6942,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -6935,17 +6962,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>BOM</t>
+          <t>ZNZ</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JRO</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -6960,7 +6987,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -6980,12 +7007,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>BOM</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -7000,12 +7027,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -7025,7 +7052,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -7045,7 +7072,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -7065,7 +7092,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -7085,11 +7112,11 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -7100,12 +7127,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -7120,16 +7147,16 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139">
@@ -7140,12 +7167,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
+          <t>HRE</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
           <t>LUN</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>EBB</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -7160,7 +7187,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -7169,18 +7196,18 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -7195,12 +7222,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -7209,7 +7236,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143">
@@ -7220,12 +7247,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -7240,12 +7267,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -7265,7 +7292,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -7285,7 +7312,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -7305,7 +7332,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>LGW</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -7325,11 +7352,11 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -7345,7 +7372,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>LGW</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -7365,11 +7392,11 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151">
@@ -7385,7 +7412,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>MGQ</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -7405,11 +7432,11 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -7425,7 +7452,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>ZNZ</t>
+          <t>MGQ</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -7440,12 +7467,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -7460,12 +7487,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>JRO</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>ZNZ</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -7480,7 +7507,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -7489,7 +7516,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
@@ -7500,7 +7527,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>LGW</t>
+          <t>JRO</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -7520,7 +7547,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -7540,7 +7567,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>LGW</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -7560,7 +7587,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>MGQ</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -7580,27 +7607,27 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -7615,17 +7642,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>MGQ</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>BOM</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -7635,37 +7662,37 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>ZNZ</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>JRO</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -7680,12 +7707,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -7705,7 +7732,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>BOM</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -7725,7 +7752,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -7745,7 +7772,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>MGQ</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -7765,11 +7792,11 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
@@ -7780,12 +7807,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -7800,12 +7827,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -7820,12 +7847,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>MGQ</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -7840,16 +7867,16 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -7860,7 +7887,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -7880,12 +7907,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>MGQ</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -7900,7 +7927,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -7915,12 +7942,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -7935,12 +7962,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>BOM</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -7955,12 +7982,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -7975,17 +8002,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -7995,17 +8022,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>MGQ</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -8015,17 +8042,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -8040,12 +8067,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -8060,12 +8087,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>BOM</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -8080,12 +8107,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>LGW</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -8100,12 +8127,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -8125,7 +8152,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -8145,7 +8172,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -8165,7 +8192,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>MGQ</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -8185,11 +8212,11 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192">
@@ -8205,7 +8232,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>ZNZ</t>
+          <t>LGW</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -8220,12 +8247,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -8240,12 +8267,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>JRO</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -8260,12 +8287,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -8280,12 +8307,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>MGQ</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -8300,16 +8327,16 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>MGQ</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="198">
@@ -8320,27 +8347,27 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>ZNZ</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -8355,12 +8382,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>JRO</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -8369,23 +8396,23 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -8395,57 +8422,57 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>LGW</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -8455,17 +8482,17 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -8475,17 +8502,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>MGQ</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -8495,37 +8522,37 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>ZNZ</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JRO</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -8540,7 +8567,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -8549,7 +8576,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210">
@@ -8560,7 +8587,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -8569,7 +8596,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211">
@@ -8580,12 +8607,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -8600,16 +8627,16 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="213">
@@ -8620,32 +8647,32 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -8655,17 +8682,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -8675,7 +8702,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -8685,7 +8712,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -8695,7 +8722,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -8705,27 +8732,27 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8735,37 +8762,37 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -8775,17 +8802,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>LGW</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -8795,17 +8822,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>MGQ</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -8815,21 +8842,21 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="224">
@@ -8840,7 +8867,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8860,12 +8887,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -8880,12 +8907,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -8900,12 +8927,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -8920,12 +8947,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>LGW</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -8940,12 +8967,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -8960,12 +8987,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>MGQ</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -8980,32 +9007,32 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>LGW</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>MGQ</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -9015,7 +9042,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -9025,27 +9052,27 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>BOM</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -9055,17 +9082,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="D235" t="n">
@@ -9075,17 +9102,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -9095,17 +9122,17 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="D237" t="n">
@@ -9115,17 +9142,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>LGW</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D238" t="n">
@@ -9135,17 +9162,17 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D239" t="n">
@@ -9155,41 +9182,41 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>MGQ</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>ZNZ</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="242">
@@ -9200,12 +9227,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D242" t="n">
@@ -9220,16 +9247,16 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244">
@@ -9240,12 +9267,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>JRO</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>BOM</t>
         </is>
       </c>
       <c r="D244" t="n">
@@ -9260,12 +9287,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D245" t="n">
@@ -9280,12 +9307,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="D246" t="n">
@@ -9300,12 +9327,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="D247" t="n">
@@ -9320,12 +9347,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="D248" t="n">
@@ -9340,12 +9367,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>ZNZ</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>JRO</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="D249" t="n">
@@ -9355,37 +9382,37 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>BOM</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>ZNZ</t>
         </is>
       </c>
       <c r="D251" t="n">
@@ -9395,17 +9422,17 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="D252" t="n">
@@ -9415,37 +9442,37 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JRO</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D254" t="n">
@@ -9455,17 +9482,17 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D255" t="n">
@@ -9475,17 +9502,17 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D256" t="n">
@@ -9495,17 +9522,17 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -9515,17 +9542,17 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D258" t="n">
@@ -9535,21 +9562,21 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>ZNZ</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>JRO</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260">
@@ -9560,7 +9587,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9580,7 +9607,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>BOM</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -9600,7 +9627,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -9609,23 +9636,23 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
           <t>BJM</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>EBB</t>
         </is>
       </c>
       <c r="D263" t="n">
@@ -9635,17 +9662,17 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
           <t>DAR</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>EBB</t>
         </is>
       </c>
       <c r="D264" t="n">
@@ -9655,7 +9682,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -9665,7 +9692,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="D265" t="n">
@@ -9675,7 +9702,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -9685,7 +9712,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="D266" t="n">
@@ -9695,7 +9722,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -9705,7 +9732,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="D267" t="n">
@@ -9715,7 +9742,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -9725,7 +9752,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="D268" t="n">
@@ -9735,7 +9762,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -9745,27 +9772,27 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>LGW</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="D270" t="n">
@@ -9775,17 +9802,17 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D271" t="n">
@@ -9795,17 +9822,17 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D272" t="n">
@@ -9815,21 +9842,21 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>MGQ</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="274">
@@ -9840,16 +9867,16 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275">
@@ -9860,12 +9887,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>ZNZ</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D275" t="n">
@@ -9880,16 +9907,16 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="277">
@@ -9900,12 +9927,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>JRO</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D277" t="n">
@@ -9920,12 +9947,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="D278" t="n">
@@ -9940,12 +9967,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>LGW</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="D279" t="n">
@@ -9960,12 +9987,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>LGW</t>
         </is>
       </c>
       <c r="D280" t="n">
@@ -9980,12 +10007,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="D281" t="n">
@@ -10000,12 +10027,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>MGQ</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="D282" t="n">
@@ -10020,16 +10047,16 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="284">
@@ -10040,12 +10067,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>ZNZ</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>JRO</t>
+          <t>MGQ</t>
         </is>
       </c>
       <c r="D284" t="n">
@@ -10055,27 +10082,27 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -10085,7 +10112,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>BOM</t>
+          <t>ZNZ</t>
         </is>
       </c>
       <c r="D286" t="n">
@@ -10095,37 +10122,37 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JRO</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D288" t="n">
@@ -10135,17 +10162,17 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D289" t="n">
@@ -10155,17 +10182,17 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>LGW</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D290" t="n">
@@ -10175,17 +10202,17 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D291" t="n">
@@ -10195,32 +10222,32 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>MGQ</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -10235,12 +10262,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -10249,23 +10276,23 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>ZNZ</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JRO</t>
         </is>
       </c>
       <c r="D295" t="n">
@@ -10280,7 +10307,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -10300,12 +10327,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>BOM</t>
         </is>
       </c>
       <c r="D297" t="n">
@@ -10320,12 +10347,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D298" t="n">
@@ -10335,17 +10362,17 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="D299" t="n">
@@ -10355,17 +10382,17 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>BOM</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="D300" t="n">
@@ -10375,27 +10402,27 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -10405,7 +10432,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="D302" t="n">
@@ -10415,7 +10442,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -10425,27 +10452,27 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D304" t="n">
@@ -10455,17 +10482,17 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="D305" t="n">
@@ -10475,17 +10502,17 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>LGW</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D306" t="n">
@@ -10495,17 +10522,17 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D307" t="n">
@@ -10515,17 +10542,17 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D308" t="n">
@@ -10535,17 +10562,17 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D309" t="n">
@@ -10555,17 +10582,17 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>MGQ</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="D310" t="n">
@@ -10575,21 +10602,21 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312">
@@ -10600,12 +10627,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>ZNZ</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D312" t="n">
@@ -10620,7 +10647,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>JRO</t>
+          <t>BOM</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -10640,7 +10667,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -10649,7 +10676,7 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="315">
@@ -10660,12 +10687,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>LGW</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="D315" t="n">
@@ -10680,12 +10707,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D316" t="n">
@@ -10700,12 +10727,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="D317" t="n">
@@ -10720,12 +10747,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>MGQ</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="D318" t="n">
@@ -10740,22 +10767,22 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>LGW</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -10765,7 +10792,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="D320" t="n">
@@ -10775,7 +10802,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -10785,7 +10812,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="D321" t="n">
@@ -10795,7 +10822,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -10805,7 +10832,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="D322" t="n">
@@ -10815,7 +10842,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -10825,7 +10852,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>MGQ</t>
         </is>
       </c>
       <c r="D323" t="n">
@@ -10835,37 +10862,37 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>ZNZ</t>
         </is>
       </c>
       <c r="D325" t="n">
@@ -10875,20 +10902,480 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>HRE</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D326" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>JRO</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D327" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>JUB</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D328" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>LGW</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D329" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>LOS</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D330" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>LUN</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>HRE</t>
+        </is>
+      </c>
+      <c r="D331" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D332" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>MGQ</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D333" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>NBO</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D334" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B326" t="inlineStr">
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>BJM</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D335" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D336" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>BJM</t>
+        </is>
+      </c>
+      <c r="D337" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="D338" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>JNB</t>
+        </is>
+      </c>
+      <c r="D339" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>JUB</t>
+        </is>
+      </c>
+      <c r="D340" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>LOS</t>
+        </is>
+      </c>
+      <c r="D341" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>LUN</t>
+        </is>
+      </c>
+      <c r="D342" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
         <is>
           <t>NBO</t>
         </is>
       </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>EBB</t>
-        </is>
-      </c>
-      <c r="D326" t="n">
+      <c r="D343" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>HRE</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D344" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>JNB</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D345" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>JUB</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D346" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>LOS</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D347" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>LUN</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>HRE</t>
+        </is>
+      </c>
+      <c r="D348" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>NBO</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D349" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10928,7 +11415,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17 — 15 sectors</t>
+          <t>2026-10-17 — 17 sectors</t>
         </is>
       </c>
     </row>
@@ -11092,8 +11579,11 @@
       <c r="B8" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="L8" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q8" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -11164,8 +11654,11 @@
       <c r="B14" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="F14" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q14" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -11230,7 +11723,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>1</v>
@@ -11248,7 +11741,7 @@
         <v>0</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>0</v>
@@ -11263,7 +11756,7 @@
         <v>0</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -11302,7 +11795,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 — 26 sectors</t>
+          <t>2026-10-18 — 29 sectors</t>
         </is>
       </c>
     </row>
@@ -11481,8 +11974,11 @@
           <t>HRE</t>
         </is>
       </c>
+      <c r="B8" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q8" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -11553,8 +12049,11 @@
           <t>LUN</t>
         </is>
       </c>
+      <c r="F14" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="Q14" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -11613,7 +12112,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C19" s="5" t="n">
         <v>1</v>
@@ -11625,7 +12124,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>1</v>
@@ -11658,7 +12157,7 @@
         <v>1</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -11697,7 +12196,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 — 8 sectors</t>
+          <t>2026-10-19 — 19 sectors</t>
         </is>
       </c>
     </row>
@@ -11794,8 +12293,14 @@
           <t>EBB</t>
         </is>
       </c>
+      <c r="C4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="G4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" s="4" t="n">
         <v>1</v>
@@ -11803,11 +12308,14 @@
       <c r="K4" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="L4" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -11816,8 +12324,11 @@
           <t>BJM</t>
         </is>
       </c>
+      <c r="B5" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q5" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -11836,8 +12347,11 @@
           <t>DAR</t>
         </is>
       </c>
+      <c r="B7" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q7" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -11860,10 +12374,10 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -11882,8 +12396,11 @@
           <t>JUB</t>
         </is>
       </c>
+      <c r="B11" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -11902,8 +12419,11 @@
           <t>LOS</t>
         </is>
       </c>
+      <c r="B13" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -11912,8 +12432,11 @@
           <t>LUN</t>
         </is>
       </c>
+      <c r="F14" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -11966,22 +12489,22 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>0</v>
@@ -11996,7 +12519,7 @@
         <v>1</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>0</v>
@@ -12005,13 +12528,13 @@
         <v>0</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -12414,19 +12937,19 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>10</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I4" s="4" t="n">
         <v>19</v>
@@ -12438,7 +12961,7 @@
         <v>12</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M4" s="4" t="n">
         <v>8</v>
@@ -12447,13 +12970,13 @@
         <v>10</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P4" s="4" t="n">
         <v>8</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>186</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5">
@@ -12463,10 +12986,10 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -12489,13 +13012,13 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O7" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -12505,13 +13028,13 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="L8" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="L8" s="4" t="n">
-        <v>6</v>
-      </c>
       <c r="Q8" s="5" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
@@ -12521,10 +13044,10 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
@@ -12547,13 +13070,13 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O11" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -12563,10 +13086,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -12576,10 +13099,10 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -12592,10 +13115,10 @@
         <v>10</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
@@ -12605,10 +13128,10 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -12644,10 +13167,10 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -12657,25 +13180,25 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>19</v>
@@ -12687,7 +13210,7 @@
         <v>12</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>8</v>
@@ -12696,13 +13219,13 @@
         <v>10</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P19" s="5" t="n">
         <v>8</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>385</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>
@@ -13516,7 +14039,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 — 17 sectors</t>
+          <t>2026-10-03 — 19 sectors</t>
         </is>
       </c>
     </row>
@@ -13683,8 +14206,11 @@
       <c r="B8" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="L8" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q8" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -13755,8 +14281,11 @@
       <c r="B14" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="F14" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q14" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -13824,7 +14353,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>1</v>
@@ -13842,7 +14371,7 @@
         <v>0</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>0</v>
@@ -13857,7 +14386,7 @@
         <v>0</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -14288,7 +14817,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05 — 21 sectors</t>
+          <t>2026-10-05 — 22 sectors</t>
         </is>
       </c>
     </row>
@@ -14528,10 +15057,10 @@
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -14599,7 +15128,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>1</v>
@@ -14632,7 +15161,7 @@
         <v>0</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/UR OCTOBER 2026/od_matrix_october2026.xlsx
+++ b/UR OCTOBER 2026/od_matrix_october2026.xlsx
@@ -29,7 +29,10 @@
     <sheet name="2026-10-17" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="2026-10-18" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="2026-10-19" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="DIVERSION_CHECK" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="2026-10-20" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="2026-10-21" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="2026-10-22" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="DIVERSION_CHECK" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -486,7 +489,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Coverage 1-19 Oct 2026 (track export window).</t>
+          <t>Coverage 1-22 Oct 2026 (track export window).</t>
         </is>
       </c>
     </row>
@@ -2875,7 +2878,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 — 22 sectors</t>
+          <t>2026-10-13 — 23 sectors</t>
         </is>
       </c>
     </row>
@@ -2985,7 +2988,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>1</v>
@@ -2997,7 +3000,7 @@
         <v>2</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -3198,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" s="5" t="n">
         <v>1</v>
@@ -3222,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -4394,7 +4397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D349"/>
+  <dimension ref="A1:D398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5336,7 +5339,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -5716,7 +5719,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -8996,7 +8999,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="231">
@@ -11082,17 +11085,17 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>ZNZ</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>JRO</t>
         </is>
       </c>
       <c r="D335" t="n">
@@ -11107,7 +11110,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -11127,12 +11130,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>BJM</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D337" t="n">
@@ -11152,7 +11155,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>BJM</t>
         </is>
       </c>
       <c r="D338" t="n">
@@ -11172,11 +11175,11 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D339" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="340">
@@ -11192,11 +11195,11 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="341">
@@ -11212,7 +11215,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="D341" t="n">
@@ -11232,7 +11235,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="D342" t="n">
@@ -11252,11 +11255,11 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="D343" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344">
@@ -11267,16 +11270,16 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="345">
@@ -11287,7 +11290,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -11296,7 +11299,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="346">
@@ -11307,7 +11310,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>JUB</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -11316,7 +11319,7 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="347">
@@ -11327,7 +11330,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>JUB</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -11347,12 +11350,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="D348" t="n">
@@ -11367,15 +11370,995 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
+          <t>LUN</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>HRE</t>
+        </is>
+      </c>
+      <c r="D349" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
           <t>NBO</t>
         </is>
       </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>EBB</t>
-        </is>
-      </c>
-      <c r="D349" t="n">
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D350" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>BJM</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D351" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D352" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>BJM</t>
+        </is>
+      </c>
+      <c r="D353" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="D354" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>HRE</t>
+        </is>
+      </c>
+      <c r="D355" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>JNB</t>
+        </is>
+      </c>
+      <c r="D356" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>JUB</t>
+        </is>
+      </c>
+      <c r="D357" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>LGW</t>
+        </is>
+      </c>
+      <c r="D358" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>MGQ</t>
+        </is>
+      </c>
+      <c r="D359" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>NBO</t>
+        </is>
+      </c>
+      <c r="D360" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>HRE</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D361" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>HRE</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>LUN</t>
+        </is>
+      </c>
+      <c r="D362" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>JNB</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D363" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>JUB</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D364" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>LGW</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D365" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>LUN</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D366" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>MGQ</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D367" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>NBO</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D368" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>BJM</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D369" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>BJM</t>
+        </is>
+      </c>
+      <c r="D370" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>BOM</t>
+        </is>
+      </c>
+      <c r="D371" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>HRE</t>
+        </is>
+      </c>
+      <c r="D372" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>JNB</t>
+        </is>
+      </c>
+      <c r="D373" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>JUB</t>
+        </is>
+      </c>
+      <c r="D374" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="D375" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>NBO</t>
+        </is>
+      </c>
+      <c r="D376" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>ZNZ</t>
+        </is>
+      </c>
+      <c r="D377" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>HRE</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>LUN</t>
+        </is>
+      </c>
+      <c r="D378" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>JNB</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D379" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>JRO</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D380" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>JUB</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D381" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>LUN</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D382" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D383" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>NBO</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D384" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>ZNZ</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>JRO</t>
+        </is>
+      </c>
+      <c r="D385" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>BJM</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D386" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>BOM</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D387" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D388" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>BJM</t>
+        </is>
+      </c>
+      <c r="D389" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="D390" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>HRE</t>
+        </is>
+      </c>
+      <c r="D391" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>JUB</t>
+        </is>
+      </c>
+      <c r="D392" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>NBO</t>
+        </is>
+      </c>
+      <c r="D393" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>HRE</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D394" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>HRE</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>LUN</t>
+        </is>
+      </c>
+      <c r="D395" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>JUB</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D396" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>LUN</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D397" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>NBO</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="D398" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11795,7 +12778,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 — 29 sectors</t>
+          <t>2026-10-18 — 30 sectors</t>
         </is>
       </c>
     </row>
@@ -12101,8 +13084,11 @@
           <t>ZNZ</t>
         </is>
       </c>
+      <c r="H18" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q18" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -12130,7 +13116,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>1</v>
@@ -12157,7 +13143,7 @@
         <v>1</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -12548,7 +13534,1147 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:Q19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="6" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 — 21 sectors</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>from \ to</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>BJM</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>BOM</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>HRE</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>JNB</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>JRO</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>JUB</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>LGW</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>LOS</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>LUN</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>MGQ</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>NBO</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>ZNZ</t>
+        </is>
+      </c>
+      <c r="Q3" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL OUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>BJM</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>BOM</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>HRE</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>JNB</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>JRO</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>JUB</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>LGW</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>LOS</t>
+        </is>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>LUN</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="Q15" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>MGQ</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>NBO</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ZNZ</t>
+        </is>
+      </c>
+      <c r="Q18" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL IN</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="5" t="n">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="6" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 — 18 sectors</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>from \ to</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>BJM</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>BOM</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>HRE</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>JNB</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>JRO</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>JUB</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>LGW</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>LOS</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>LUN</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>MGQ</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>NBO</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>ZNZ</t>
+        </is>
+      </c>
+      <c r="Q3" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL OUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>BJM</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>BOM</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>HRE</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>JNB</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>JRO</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>JUB</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>LGW</t>
+        </is>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>LOS</t>
+        </is>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>LUN</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>MGQ</t>
+        </is>
+      </c>
+      <c r="Q16" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>NBO</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ZNZ</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL IN</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="5" t="n">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="6" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 — 17 sectors</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>from \ to</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>BJM</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>BOM</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>HRE</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>JNB</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>JRO</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>JUB</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>LGW</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>LOS</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>LUN</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>MGQ</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>NBO</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>ZNZ</t>
+        </is>
+      </c>
+      <c r="Q3" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL OUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>BJM</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>BOM</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>HRE</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>JNB</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>JRO</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>JUB</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>LGW</t>
+        </is>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>LOS</t>
+        </is>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>LUN</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="Q15" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>MGQ</t>
+        </is>
+      </c>
+      <c r="Q16" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>NBO</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ZNZ</t>
+        </is>
+      </c>
+      <c r="Q18" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL IN</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12798,6 +14924,174 @@
         </is>
       </c>
       <c r="H6" t="inlineStr">
+        <is>
+          <t>suffixed callsign; sector never planned for this flight number (diversion/off-plan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>UGD722D</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>HRE-&gt;LUN</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EBB-HRE, HRE-LUN, LUN-EBB</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>UR722-423a7574.csv</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>suffixed callsign</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>UGD722D</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LUN-&gt;EBB</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EBB-HRE, HRE-LUN, LUN-EBB</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2232</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>UR722-423ae45f.csv</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>suffixed callsign</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>UGD722X</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EBB-&gt;HRE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EBB-HRE, HRE-LUN, LUN-EBB</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0451</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>UNKNOWN-423bc735.csv</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>suffixed callsign</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>UGD722X</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>HRE-&gt;EBB</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EBB-HRE, HRE-LUN, LUN-EBB</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0904</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>UNKNOWN-423c636e.csv</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>suffixed callsign; sector never planned for this flight number (diversion/off-plan)</t>
         </is>
@@ -12839,7 +15133,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>October 2026 (1-19 Oct) — all sectors</t>
+          <t>October 2026 (1-22 Oct) — all sectors</t>
         </is>
       </c>
     </row>
@@ -12937,25 +15231,25 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>12</v>
@@ -12964,19 +15258,19 @@
         <v>12</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>191</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5">
@@ -12986,10 +15280,10 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -12999,10 +15293,10 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -13012,13 +15306,13 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O7" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -13028,13 +15322,13 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -13044,10 +15338,10 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -13057,10 +15351,10 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -13070,13 +15364,13 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O11" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -13086,10 +15380,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -13112,13 +15406,13 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>12</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -13128,10 +15422,10 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -13141,10 +15435,10 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
@@ -13154,10 +15448,10 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -13167,10 +15461,10 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
@@ -13180,52 +15474,52 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>191</v>
+        <v>218</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K19" s="5" t="n">
         <v>12</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>413</v>
+        <v>473</v>
       </c>
     </row>
   </sheetData>
@@ -14039,7 +16333,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 — 19 sectors</t>
+          <t>2026-10-03 — 20 sectors</t>
         </is>
       </c>
     </row>
@@ -14158,10 +16452,10 @@
         <v>1</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -14380,13 +16674,13 @@
         <v>1</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -14425,7 +16719,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04 — 24 sectors</t>
+          <t>2026-10-04 — 25 sectors</t>
         </is>
       </c>
     </row>
@@ -14541,7 +16835,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O4" s="4" t="n">
         <v>2</v>
@@ -14550,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -14769,7 +17063,7 @@
         <v>0</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O19" s="5" t="n">
         <v>2</v>
@@ -14778,7 +17072,7 @@
         <v>1</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
